--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487487_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487487_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.5512</v>
+        <v>10.6245</v>
       </c>
       <c r="E2" t="n">
-        <v>9.538500000000001</v>
+        <v>8.531599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0127</v>
+        <v>2.0929</v>
       </c>
       <c r="G2" t="n">
         <v>4.8199</v>
@@ -610,13 +610,13 @@
         <v>3.1336</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3972</v>
+        <v>1.4705</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8556</v>
+        <v>0.8487</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5416</v>
+        <v>0.6218</v>
       </c>
       <c r="V2" t="n">
         <v>2.3756</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9302</v>
+        <v>2.7863</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8317</v>
+        <v>1.8482</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0985</v>
+        <v>0.9381</v>
       </c>
       <c r="G3" t="n">
         <v>-1.9006</v>
@@ -688,13 +688,13 @@
         <v>3.917</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0474</v>
+        <v>1.9035</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2327</v>
+        <v>1.2492</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8147</v>
+        <v>0.6543</v>
       </c>
       <c r="V3" t="n">
         <v>1.2166</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6246</v>
+        <v>2.0153</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6166</v>
+        <v>0.6331</v>
       </c>
       <c r="F4" t="n">
-        <v>1.008</v>
+        <v>1.3822</v>
       </c>
       <c r="G4" t="n">
         <v>-1.0454</v>
@@ -766,13 +766,13 @@
         <v>1.5668</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1134</v>
+        <v>0.2773</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0129</v>
+        <v>0.0035</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1005</v>
+        <v>0.2738</v>
       </c>
       <c r="V4" t="n">
         <v>1.2166</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.3475</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3171</v>
+        <v>-1.0959</v>
       </c>
       <c r="F5" t="n">
-        <v>1.39</v>
+        <v>1.4434</v>
       </c>
       <c r="G5" t="n">
         <v>0.1156</v>
@@ -844,13 +844,13 @@
         <v>0.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1602</v>
+        <v>0.1144</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3564</v>
+        <v>-0.1353</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1962</v>
+        <v>0.2497</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6659</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. SABATER MARTINEZ</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0549</v>
+        <v>0.0132</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5088</v>
+        <v>1.0551</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4539</v>
+        <v>-1.0419</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.0758</v>
+        <v>-3.1031</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.5152</v>
+        <v>-1.4409</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4394</v>
+        <v>-1.6622</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1083</v>
+        <v>1.2112</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6788999999999999</v>
+        <v>1.2776</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5706</v>
+        <v>-0.0664</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9676</v>
+        <v>-4.3144</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8363</v>
+        <v>-2.7185</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1313</v>
+        <v>-1.5958</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.7626</v>
+        <v>1.1751</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1336</v>
+        <v>-2.3502</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3709</v>
+        <v>3.5253</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8507</v>
+        <v>1.2754</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7079</v>
+        <v>0.9775</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1427</v>
+        <v>0.2979</v>
       </c>
       <c r="V6" t="n">
-        <v>2.0427</v>
+        <v>0.6659</v>
       </c>
       <c r="W6" t="n">
-        <v>2.0427</v>
+        <v>1.2166</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2747</v>
+        <v>-0.7753</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0512</v>
+        <v>-2.8301</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7765</v>
+        <v>2.0548</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8515</v>
@@ -1000,13 +1000,13 @@
         <v>3.3294</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4166</v>
+        <v>1.916</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4911</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>1.9255</v>
+        <v>1.2038</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0564</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>G. SABATER MARTINEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6159</v>
+        <v>-0.8335</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5864</v>
+        <v>-0.3529</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2023</v>
+        <v>-0.4806</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.1031</v>
+        <v>-2.0758</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4409</v>
+        <v>-2.5152</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6622</v>
+        <v>0.4394</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2112</v>
+        <v>-0.1083</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2776</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0664</v>
+        <v>0.5706</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.3144</v>
+        <v>-1.9676</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.7185</v>
+        <v>-1.8363</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5958</v>
+        <v>-0.1313</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1751</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3502</v>
+        <v>-3.1336</v>
       </c>
       <c r="R8" t="n">
-        <v>3.5253</v>
+        <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6462</v>
+        <v>0.9623</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5087</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1375</v>
+        <v>0.116</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6659</v>
+        <v>2.0427</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2166</v>
+        <v>2.0427</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3366</v>
+        <v>-1.0458</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.291</v>
+        <v>-2.0269</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9544</v>
+        <v>0.9811</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1364</v>
@@ -1156,13 +1156,13 @@
         <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2198</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3982</v>
+        <v>-0.1341</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1784</v>
+        <v>0.2051</v>
       </c>
       <c r="V9" t="n">
         <v>0.3905</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4849</v>
+        <v>-1.2196</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4481</v>
+        <v>-0.263</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0368</v>
+        <v>-0.9566</v>
       </c>
       <c r="G10" t="n">
         <v>-3.9029</v>
@@ -1234,13 +1234,13 @@
         <v>1.9585</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3447</v>
+        <v>0.9206</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3982</v>
+        <v>0.7869</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0535</v>
+        <v>0.1337</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7667</v>
+        <v>-2.2666</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8397</v>
+        <v>-1.4733</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.927</v>
+        <v>-0.7933</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4192</v>
@@ -1312,13 +1312,13 @@
         <v>2.3502</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2608</v>
+        <v>0.7609</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2247</v>
+        <v>0.5911</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0362</v>
+        <v>0.1698</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.755000000000003</v>
+        <v>9.646000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.134900000000001</v>
+        <v>4.0259</v>
       </c>
       <c r="F12" t="n">
-        <v>5.620100000000001</v>
+        <v>5.6201</v>
       </c>
       <c r="G12" t="n">
         <v>-10.4994</v>
@@ -1363,7 +1363,7 @@
         <v>-8.791099999999998</v>
       </c>
       <c r="J12" t="n">
-        <v>8.6768</v>
+        <v>8.676799999999998</v>
       </c>
       <c r="K12" t="n">
         <v>11.5356</v>
@@ -1390,13 +1390,13 @@
         <v>22.5226</v>
       </c>
       <c r="S12" t="n">
-        <v>8.780799999999999</v>
+        <v>9.671899999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>4.855</v>
+        <v>5.746</v>
       </c>
       <c r="U12" t="n">
-        <v>3.9258</v>
+        <v>3.9259</v>
       </c>
       <c r="V12" t="n">
         <v>5.5773</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7977</v>
+        <v>5.0097</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3184</v>
+        <v>3.4207</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4793</v>
+        <v>1.589</v>
       </c>
       <c r="G13" t="n">
         <v>4.2802</v>
@@ -1468,13 +1468,13 @@
         <v>2.546</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3823</v>
+        <v>-1.1702</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.517</v>
+        <v>-0.4146</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8653</v>
+        <v>-0.7556</v>
       </c>
       <c r="V13" t="n">
         <v>0.3329</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1957</v>
+        <v>3.3026</v>
       </c>
       <c r="E14" t="n">
         <v>2.785</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4107</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>2.6309</v>
@@ -1546,13 +1546,13 @@
         <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1391</v>
+        <v>-1.0322</v>
       </c>
       <c r="T14" t="n">
         <v>-0.1782</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9609</v>
+        <v>-0.854</v>
       </c>
       <c r="V14" t="n">
         <v>0.3329</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7941</v>
+        <v>1.9305</v>
       </c>
       <c r="E15" t="n">
         <v>1.2643</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5298</v>
+        <v>0.6662</v>
       </c>
       <c r="G15" t="n">
         <v>4.829</v>
@@ -1624,13 +1624,13 @@
         <v>3.5253</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3886</v>
+        <v>-1.2521</v>
       </c>
       <c r="T15" t="n">
         <v>-0.5476</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.841</v>
+        <v>-0.7046</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2754</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0366</v>
+        <v>0.9637</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9459</v>
+        <v>0.8435</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0907</v>
+        <v>0.1202</v>
       </c>
       <c r="G16" t="n">
         <v>1.93</v>
@@ -1702,13 +1702,13 @@
         <v>2.9377</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.7669</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0723</v>
+        <v>-0.1747</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6218</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-2.1578</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2492</v>
+        <v>-0.1662</v>
       </c>
       <c r="E17" t="n">
         <v>1.0028</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.252</v>
+        <v>-1.169</v>
       </c>
       <c r="G17" t="n">
         <v>0.7831</v>
@@ -1780,13 +1780,13 @@
         <v>0.5875</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4032</v>
+        <v>-0.3202</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2844</v>
+        <v>-0.2014</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2166</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5639</v>
+        <v>-0.4827</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8571</v>
+        <v>-1.7547</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2932</v>
+        <v>1.272</v>
       </c>
       <c r="G18" t="n">
         <v>0.2485</v>
@@ -1858,13 +1858,13 @@
         <v>1.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.029</v>
+        <v>0.0522</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3388</v>
+        <v>-0.2364</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3098</v>
+        <v>0.2886</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4968</v>
+        <v>-1.4701</v>
       </c>
       <c r="E19" t="n">
         <v>-1.0386</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4582</v>
+        <v>-0.4315</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3396</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.178</v>
+        <v>-0.1513</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1186</v>
+        <v>-0.0919</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Y. PINAS</t>
+          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8767</v>
+        <v>-2.233</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6523</v>
+        <v>0.2375</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2245</v>
+        <v>-2.4705</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2204</v>
+        <v>1.2051</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.867</v>
+        <v>-0.5835</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3534</v>
+        <v>1.7886</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2598</v>
+        <v>2.6103</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2194</v>
+        <v>0.706</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0404</v>
+        <v>1.9043</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4801</v>
+        <v>-1.4052</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0864</v>
+        <v>-1.2895</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3938</v>
+        <v>-0.1157</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R20" t="n">
         <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2077</v>
+        <v>-0.3207</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0465</v>
+        <v>-0.3188</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1613</v>
+        <v>-0.0019</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1152</v>
+        <v>-1.159</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1152</v>
+        <v>-2.0427</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
+          <t>Y. PINAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9961</v>
+        <v>-2.31</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8515</v>
+        <v>-2.0616</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8475</v>
+        <v>-0.2484</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2051</v>
+        <v>-1.2204</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5835</v>
+        <v>-0.867</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7886</v>
+        <v>-0.3534</v>
       </c>
       <c r="J21" t="n">
-        <v>2.6103</v>
+        <v>0.2598</v>
       </c>
       <c r="K21" t="n">
-        <v>0.706</v>
+        <v>0.2194</v>
       </c>
       <c r="L21" t="n">
-        <v>1.9043</v>
+        <v>0.0404</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4052</v>
+        <v>-1.4801</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2895</v>
+        <v>-1.0864</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1157</v>
+        <v>-0.3938</v>
       </c>
       <c r="P21" t="n">
+        <v>-0.9792</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-1.9585</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-2.9377</v>
       </c>
       <c r="R21" t="n">
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0837</v>
+        <v>-0.2256</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2952</v>
+        <v>-0.3629</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3789</v>
+        <v>0.1373</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.159</v>
+        <v>0.1152</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.0427</v>
+        <v>0.1152</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8158</v>
+        <v>-3.6737</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.2074</v>
+        <v>-4.7981</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3917</v>
+        <v>1.1244</v>
       </c>
       <c r="G22" t="n">
         <v>0.9134</v>
@@ -2170,13 +2170,13 @@
         <v>1.9585</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8122</v>
+        <v>-0.6702</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7128</v>
+        <v>-0.3035</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0994</v>
+        <v>-0.3667</v>
       </c>
       <c r="V22" t="n">
         <v>-0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5444</v>
+        <v>-3.7581</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0511</v>
+        <v>-1.6418</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4933</v>
+        <v>-2.1163</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4697</v>
@@ -2248,13 +2248,13 @@
         <v>0.9792</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5252</v>
+        <v>-0.7388</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0098</v>
+        <v>-0.6005</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5154</v>
+        <v>-0.1384</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5495</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0361</v>
+        <v>-4.5032</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9813</v>
+        <v>-3.8789</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0548</v>
+        <v>-0.6243</v>
       </c>
       <c r="G24" t="n">
         <v>-3.2912</v>
@@ -2326,13 +2326,13 @@
         <v>0.5875</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3531</v>
+        <v>-0.8203</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7128</v>
+        <v>-0.6105</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6403</v>
+        <v>-0.2098</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.754900000000001</v>
+        <v>-7.390500000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.619899999999999</v>
+        <v>-5.619899999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1349</v>
+        <v>-1.7706</v>
       </c>
       <c r="G25" t="n">
         <v>10.4993</v>
@@ -2374,7 +2374,7 @@
         <v>1.708</v>
       </c>
       <c r="I25" t="n">
-        <v>8.7911</v>
+        <v>8.791099999999998</v>
       </c>
       <c r="J25" t="n">
         <v>19.1764</v>
@@ -2383,7 +2383,7 @@
         <v>13.2439</v>
       </c>
       <c r="L25" t="n">
-        <v>5.932300000000001</v>
+        <v>5.932299999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-8.677</v>
@@ -2404,13 +2404,13 @@
         <v>17.6261</v>
       </c>
       <c r="S25" t="n">
-        <v>-8.780799999999999</v>
+        <v>-7.416300000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.9258</v>
+        <v>-3.9259</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.8549</v>
+        <v>-3.490599999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-5.5773</v>
